--- a/docs/StructureDefinition-PASportObservationSoftLeanMass.xlsx
+++ b/docs/StructureDefinition-PASportObservationSoftLeanMass.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T05:34:23+08:00</t>
+    <t>2026-02-28T07:16:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationSoftLeanMass.xlsx
+++ b/docs/StructureDefinition-PASportObservationSoftLeanMass.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T07:16:04+08:00</t>
+    <t>2026-02-28T23:13:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationSoftLeanMass.xlsx
+++ b/docs/StructureDefinition-PASportObservationSoftLeanMass.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T23:13:53+08:00</t>
+    <t>2026-03-01T19:25:35+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationSoftLeanMass.xlsx
+++ b/docs/StructureDefinition-PASportObservationSoftLeanMass.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:25:35+08:00</t>
+    <t>2026-03-02T02:26:08+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationSoftLeanMass.xlsx
+++ b/docs/StructureDefinition-PASportObservationSoftLeanMass.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3633" uniqueCount="664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3633" uniqueCount="666">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T02:26:08+08:00</t>
+    <t>2026-04-02T13:32:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,10 +269,10 @@
 </t>
   </si>
   <si>
-    <t>Measurements and simple assertions</t>
-  </si>
-  <si>
-    <t>Measurements and simple assertions made about a patient, device or other subject.</t>
+    <t>通用檢驗檢查結果或發現的測量和簡單聲明</t>
+  </si>
+  <si>
+    <t>關於患者的通用檢驗檢查結果測量和簡單聲明，包括由設備或醫護人員觀察到的發現。</t>
   </si>
   <si>
     <t>Used for simple observations such as device measurements, laboratory atomic results, vital signs, height, weight, smoking status, comments, etc.  Other resources are used to provide context for observations such as laboratory reports, etc.</t>
@@ -346,10 +346,10 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+    <t>創建此內容所依據的一組規則</t>
+  </si>
+  <si>
+    <t>構建 resource 時遵循的一系列規則的參照，在處理內容時必須理解這些規則。通常這是對 IG 所定義之特殊規則及其他 profiles 的參照。</t>
   </si>
   <si>
     <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
@@ -380,7 +380,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -520,10 +520,10 @@
 </t>
   </si>
   <si>
-    <t>Fulfills plan, proposal or order</t>
-  </si>
-  <si>
-    <t>A plan, proposal or order that is fulfilled in whole or in part by this event.  For example, a MedicationRequest may require a patient to have laboratory test performed before  it is dispensed.</t>
+    <t>檢驗檢查的依據</t>
+  </si>
+  <si>
+    <t>產生此檢驗檢查的計畫或請求。</t>
   </si>
   <si>
     <t>Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
@@ -549,10 +549,10 @@
 </t>
   </si>
   <si>
-    <t>Part of referenced event</t>
-  </si>
-  <si>
-    <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
+    <t>作為較大項目的一部分</t>
+  </si>
+  <si>
+    <t>表示此檢驗檢查是其他資源的一部分，例如：用藥給藥、調劑、用藥聲明、處置、免疫接種或影像檢查。</t>
   </si>
   <si>
     <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
@@ -573,7 +573,7 @@
     <t>registered | preliminary | final | amended +</t>
   </si>
   <si>
-    <t>The status of the result value.</t>
+    <t>該項檢驗檢查的狀態。</t>
   </si>
   <si>
     <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
@@ -613,10 +613,10 @@
 </t>
   </si>
   <si>
-    <t>Classification of  type of observation</t>
-  </si>
-  <si>
-    <t>A code that classifies the general type of observation being made.</t>
+    <t>檢驗檢查的分類</t>
+  </si>
+  <si>
+    <t>檢驗檢查的分類。</t>
   </si>
   <si>
     <t>In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
@@ -628,7 +628,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:$this}
@@ -654,7 +654,13 @@
 </t>
   </si>
   <si>
-    <t>此slice綁定的值集之綁定強度雖為最高強度「要求使用(Requird)」，但因slice之特性，其不會限制僅能填此值集中的代碼，故在實作時也可使用其他值集的代碼。</t>
+    <t>臺灣核心分類</t>
+  </si>
+  <si>
+    <t>臺灣核心檢驗檢查分類。</t>
+  </si>
+  <si>
+    <t>此 slice 綁定的值集之綁定強度雖為最高強度「要求使用 (Requird)」，但因 slice 之特性，其不會限制僅能填此值集中的代碼，故在實作時也可使用其他值集的代碼。</t>
   </si>
   <si>
     <t>https://twcore.mohw.gov.tw/ig/twcore/ValueSet/category-code-tw</t>
@@ -920,10 +926,10 @@
     <t>肌肉量</t>
   </si>
   <si>
-    <t>A concept that may be defined by a formal reference to a terminology or ontology or may be provided by text.</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+    <t>描述該檢驗檢查所測量的內容</t>
+  </si>
+  <si>
+    <t>*All* code-value and, if present, component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
   </si>
   <si>
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
@@ -935,14 +941,22 @@
     <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE</t>
-  </si>
-  <si>
-    <t>CD</t>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>&lt; 363787002 |Observable entity| OR &lt; 386053000 |Evaluation procedure|</t>
+  </si>
+  <si>
+    <t>OBX-3</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>116680003 |Is a|</t>
   </si>
   <si>
     <t>Observation.code.id</t>
@@ -979,12 +993,6 @@
     <t>允許代碼系統中的替代編碼，以及翻譯到其他編碼系統。</t>
   </si>
   <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
     <t>Observation.code.coding.id</t>
   </si>
   <si>
@@ -1097,7 +1105,7 @@
     <t>量測對象</t>
   </si>
   <si>
-    <t>The patient, or group of patients, location, or device this observation is about and into whose record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
+    <t>檢驗檢查關注的主體 (如患者、群組、設備或位置)。</t>
   </si>
   <si>
     <t>One would expect this element to be a cardinality of 1..1. The only circumstance in which the subject can be missing is when the observation is made by a device that does not know the patient. In this case, the observation SHALL be matched to a patient through some context/channel matching technique, and at this point, the observation should be updated.</t>
@@ -1207,7 +1215,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1218,9 +1226,6 @@
   </si>
   <si>
     <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
-  </si>
-  <si>
-    <t>OBX-3</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -1237,10 +1242,10 @@
 </t>
   </si>
   <si>
-    <t>Healthcare event during which this observation is made</t>
-  </si>
-  <si>
-    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) during which this observation is made.</t>
+    <t>與此檢驗檢查相關的就醫事件</t>
+  </si>
+  <si>
+    <t>此檢驗檢查是在哪個就醫情境產生的。</t>
   </si>
   <si>
     <t>This will typically be the encounter the event occurred within, but some events may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter (e.g. pre-admission laboratory tests).</t>
@@ -1272,10 +1277,10 @@
 PeriodTiminginstant</t>
   </si>
   <si>
-    <t>Clinically relevant time/time-period for observation</t>
-  </si>
-  <si>
-    <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
+    <t>檢驗檢查的時間或時段</t>
+  </si>
+  <si>
+    <t>檢驗檢查進行的時間點或時間段。</t>
   </si>
   <si>
     <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
@@ -1331,7 +1336,7 @@
     <t>量測人員</t>
   </si>
   <si>
-    <t>Who was responsible for asserting the observed value as "true".</t>
+    <t>執行或負責檢驗檢查的人員。</t>
   </si>
   <si>
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
@@ -1377,10 +1382,10 @@
 </t>
   </si>
   <si>
-    <t>Actual result</t>
-  </si>
-  <si>
-    <t>The information determined as a result of making the observation, if the information has a simple value.</t>
+    <t>檢驗檢查的結果值</t>
+  </si>
+  <si>
+    <t>檢驗檢查或觀察的實際結果。</t>
   </si>
   <si>
     <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
@@ -1595,7 +1600,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1627,7 +1632,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1726,10 +1731,10 @@
 </t>
   </si>
   <si>
-    <t>Specimen used for this observation</t>
-  </si>
-  <si>
-    <t>The specimen that was used when this observation was made.</t>
+    <t>檢驗檢查的檢體</t>
+  </si>
+  <si>
+    <t>進行檢驗檢查的檢體。</t>
   </si>
   <si>
     <t>Should only be used if not implicit in code found in `Observation.code`.  Observations are not made on specimens themselves; they are made on a subject, but in many cases by the means of a specimen. Note that although specimens are often involved, they are not always tracked and reported explicitly. Also note that observation resources may be used in contexts that track the specimen explicitly (e.g. Diagnostic Report).</t>
@@ -1750,7 +1755,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1830,7 +1835,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1880,7 +1885,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1916,7 +1921,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1957,10 +1962,10 @@
 </t>
   </si>
   <si>
-    <t>Related resource that belongs to the Observation group</t>
-  </si>
-  <si>
-    <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
+    <t>包含的相關檢驗檢查</t>
+  </si>
+  <si>
+    <t>與此檢驗檢查相關聯的其他檢驗檢查或問卷回應。</t>
   </si>
   <si>
     <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
@@ -1979,10 +1984,10 @@
 </t>
   </si>
   <si>
-    <t>Related measurements the observation is made from</t>
-  </si>
-  <si>
-    <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
+    <t>觀察來源或依據</t>
+  </si>
+  <si>
+    <t>用於獲取此觀察結果的參考資源，如：來源觀察、文件引用、問卷回應等。</t>
   </si>
   <si>
     <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
@@ -2031,18 +2036,15 @@
   </si>
   <si>
     <t>*All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR  &lt; 386053000 |Evaluation procedure|</t>
   </si>
   <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
     <t>Observation.component.value[x]</t>
   </si>
   <si>
@@ -2051,6 +2053,9 @@
   </si>
   <si>
     <t>Actual component result</t>
+  </si>
+  <si>
+    <t>The information determined as a result of making the observation, if the information has a simple value.</t>
   </si>
   <si>
     <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
@@ -2425,7 +2430,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="114.32421875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="116.8203125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="52.62109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -4287,10 +4292,10 @@
         <v>203</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>193</v>
@@ -4324,10 +4329,10 @@
         <v>181</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -4380,10 +4385,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4406,13 +4411,13 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4463,7 +4468,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4487,7 +4492,7 @@
         <v>20</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>20</v>
@@ -4498,10 +4503,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4530,7 +4535,7 @@
         <v>139</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>141</v>
@@ -4571,10 +4576,10 @@
         <v>20</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>20</v>
@@ -4583,7 +4588,7 @@
         <v>198</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4607,7 +4612,7 @@
         <v>20</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>20</v>
@@ -4618,10 +4623,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4644,19 +4649,19 @@
         <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -4705,7 +4710,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4726,10 +4731,10 @@
         <v>20</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>20</v>
@@ -4740,10 +4745,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4766,13 +4771,13 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4823,7 +4828,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4847,7 +4852,7 @@
         <v>20</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>20</v>
@@ -4858,10 +4863,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4890,7 +4895,7 @@
         <v>139</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>141</v>
@@ -4931,10 +4936,10 @@
         <v>20</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>20</v>
@@ -4943,7 +4948,7 @@
         <v>198</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4967,7 +4972,7 @@
         <v>20</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>20</v>
@@ -4978,10 +4983,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5007,16 +5012,16 @@
         <v>106</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -5026,7 +5031,7 @@
         <v>20</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>20</v>
@@ -5065,7 +5070,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5086,10 +5091,10 @@
         <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>20</v>
@@ -5100,10 +5105,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5126,16 +5131,16 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5185,7 +5190,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5206,10 +5211,10 @@
         <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>20</v>
@@ -5220,10 +5225,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5249,14 +5254,14 @@
         <v>112</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -5266,7 +5271,7 @@
         <v>20</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>20</v>
@@ -5305,7 +5310,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5326,10 +5331,10 @@
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>20</v>
@@ -5340,10 +5345,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5366,17 +5371,17 @@
         <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -5386,7 +5391,7 @@
         <v>20</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>20</v>
@@ -5425,7 +5430,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5446,10 +5451,10 @@
         <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>20</v>
@@ -5460,10 +5465,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5486,19 +5491,19 @@
         <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -5547,7 +5552,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5568,10 +5573,10 @@
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>20</v>
@@ -5582,10 +5587,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5608,19 +5613,19 @@
         <v>93</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -5669,7 +5674,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5690,10 +5695,10 @@
         <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>20</v>
@@ -5704,14 +5709,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5727,22 +5732,22 @@
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
         <v>190</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -5770,10 +5775,10 @@
         <v>116</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>20</v>
@@ -5791,7 +5796,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>92</v>
@@ -5800,36 +5805,36 @@
         <v>92</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>296</v>
+        <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>20</v>
+        <v>298</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>20</v>
+        <v>299</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>20</v>
+        <v>302</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>20</v>
+        <v>303</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5852,13 +5857,13 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5909,7 +5914,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5933,7 +5938,7 @@
         <v>20</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
@@ -5944,10 +5949,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5973,10 +5978,10 @@
         <v>138</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6015,10 +6020,10 @@
         <v>20</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>20</v>
@@ -6027,7 +6032,7 @@
         <v>198</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -6062,10 +6067,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6085,22 +6090,22 @@
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -6149,7 +6154,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6158,7 +6163,7 @@
         <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>296</v>
+        <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>104</v>
@@ -6170,10 +6175,10 @@
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>310</v>
+        <v>229</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>311</v>
+        <v>230</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>20</v>
@@ -6184,10 +6189,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6210,13 +6215,13 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6267,7 +6272,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6291,7 +6296,7 @@
         <v>20</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
@@ -6302,10 +6307,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6331,13 +6336,13 @@
         <v>138</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6375,10 +6380,10 @@
         <v>20</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>20</v>
@@ -6387,7 +6392,7 @@
         <v>198</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6422,10 +6427,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6451,16 +6456,16 @@
         <v>106</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -6470,7 +6475,7 @@
         <v>20</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>20</v>
@@ -6509,7 +6514,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6530,10 +6535,10 @@
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>20</v>
@@ -6544,10 +6549,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6570,16 +6575,16 @@
         <v>93</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6629,7 +6634,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6650,10 +6655,10 @@
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>20</v>
@@ -6664,10 +6669,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6693,14 +6698,14 @@
         <v>112</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -6710,7 +6715,7 @@
         <v>20</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>20</v>
@@ -6749,7 +6754,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6770,10 +6775,10 @@
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>20</v>
@@ -6784,10 +6789,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6810,17 +6815,17 @@
         <v>93</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -6830,7 +6835,7 @@
         <v>20</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>20</v>
@@ -6869,7 +6874,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6890,10 +6895,10 @@
         <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
@@ -6904,10 +6909,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6930,19 +6935,19 @@
         <v>93</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6991,7 +6996,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7012,10 +7017,10 @@
         <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>20</v>
@@ -7026,10 +7031,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7052,19 +7057,19 @@
         <v>93</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -7113,7 +7118,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7134,10 +7139,10 @@
         <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>20</v>
@@ -7148,10 +7153,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7174,19 +7179,19 @@
         <v>93</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -7235,7 +7240,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7250,19 +7255,19 @@
         <v>104</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>20</v>
@@ -7270,10 +7275,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7296,13 +7301,13 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7353,7 +7358,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7377,7 +7382,7 @@
         <v>20</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>20</v>
@@ -7388,10 +7393,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7420,7 +7425,7 @@
         <v>139</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>141</v>
@@ -7461,10 +7466,10 @@
         <v>20</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>20</v>
@@ -7473,7 +7478,7 @@
         <v>198</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7497,7 +7502,7 @@
         <v>20</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>20</v>
@@ -7508,10 +7513,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7534,16 +7539,16 @@
         <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7593,7 +7598,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7602,7 +7607,7 @@
         <v>92</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>104</v>
@@ -7628,10 +7633,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7657,13 +7662,13 @@
         <v>106</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7689,13 +7694,13 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -7713,7 +7718,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7748,10 +7753,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7777,13 +7782,13 @@
         <v>150</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7833,7 +7838,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7857,7 +7862,7 @@
         <v>20</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
@@ -7868,10 +7873,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7894,16 +7899,16 @@
         <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7953,7 +7958,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7988,10 +7993,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8014,16 +8019,16 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8073,7 +8078,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8094,13 +8099,13 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>388</v>
+        <v>300</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>20</v>
@@ -8108,14 +8113,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -8134,19 +8139,19 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -8195,7 +8200,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8210,19 +8215,19 @@
         <v>104</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>20</v>
@@ -8230,14 +8235,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -8256,19 +8261,19 @@
         <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -8317,7 +8322,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8332,19 +8337,19 @@
         <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>20</v>
@@ -8352,10 +8357,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8378,16 +8383,16 @@
         <v>93</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8437,7 +8442,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8458,13 +8463,13 @@
         <v>20</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>20</v>
@@ -8472,10 +8477,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8498,17 +8503,17 @@
         <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -8557,7 +8562,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8572,19 +8577,19 @@
         <v>104</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>20</v>
@@ -8592,10 +8597,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8618,13 +8623,13 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8675,7 +8680,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8699,7 +8704,7 @@
         <v>20</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>20</v>
@@ -8710,10 +8715,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8742,7 +8747,7 @@
         <v>139</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>141</v>
@@ -8783,10 +8788,10 @@
         <v>20</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>20</v>
@@ -8795,7 +8800,7 @@
         <v>198</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8819,7 +8824,7 @@
         <v>20</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>20</v>
@@ -8830,10 +8835,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8856,16 +8861,16 @@
         <v>93</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8915,7 +8920,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8924,7 +8929,7 @@
         <v>92</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>104</v>
@@ -8950,10 +8955,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8979,13 +8984,13 @@
         <v>106</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9011,13 +9016,13 @@
         <v>20</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>20</v>
@@ -9035,7 +9040,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9070,10 +9075,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9099,13 +9104,13 @@
         <v>150</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9155,7 +9160,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9179,7 +9184,7 @@
         <v>20</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>20</v>
@@ -9190,10 +9195,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9216,16 +9221,16 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9275,7 +9280,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9310,10 +9315,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9336,19 +9341,19 @@
         <v>93</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
@@ -9385,17 +9390,17 @@
         <v>20</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9404,7 +9409,7 @@
         <v>92</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>104</v>
@@ -9413,30 +9418,30 @@
         <v>20</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>20</v>
@@ -9458,19 +9463,19 @@
         <v>93</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -9519,7 +9524,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9528,7 +9533,7 @@
         <v>92</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>104</v>
@@ -9537,27 +9542,27 @@
         <v>20</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9580,13 +9585,13 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9637,7 +9642,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9661,7 +9666,7 @@
         <v>20</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>20</v>
@@ -9672,10 +9677,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9704,7 +9709,7 @@
         <v>139</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>141</v>
@@ -9745,10 +9750,10 @@
         <v>20</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>20</v>
@@ -9757,7 +9762,7 @@
         <v>198</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9781,7 +9786,7 @@
         <v>20</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>20</v>
@@ -9792,10 +9797,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9818,19 +9823,19 @@
         <v>93</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
@@ -9879,7 +9884,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9900,10 +9905,10 @@
         <v>20</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>20</v>
@@ -9914,10 +9919,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9943,20 +9948,20 @@
         <v>112</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q63" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="R63" t="s" s="2">
         <v>20</v>
@@ -9980,10 +9985,10 @@
         <v>181</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>20</v>
@@ -10001,7 +10006,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10022,10 +10027,10 @@
         <v>20</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>20</v>
@@ -10036,10 +10041,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10062,17 +10067,17 @@
         <v>93</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>20</v>
@@ -10121,7 +10126,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10142,10 +10147,10 @@
         <v>20</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>20</v>
@@ -10156,10 +10161,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10185,14 +10190,14 @@
         <v>106</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>20</v>
@@ -10202,7 +10207,7 @@
         <v>20</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>20</v>
@@ -10241,7 +10246,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10250,7 +10255,7 @@
         <v>92</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>104</v>
@@ -10262,10 +10267,10 @@
         <v>20</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>20</v>
@@ -10276,10 +10281,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10305,16 +10310,16 @@
         <v>112</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -10324,7 +10329,7 @@
         <v>20</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>20</v>
@@ -10363,7 +10368,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10384,10 +10389,10 @@
         <v>20</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>20</v>
@@ -10398,10 +10403,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10427,16 +10432,16 @@
         <v>203</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>20</v>
@@ -10461,13 +10466,13 @@
         <v>20</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>20</v>
@@ -10485,7 +10490,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10494,7 +10499,7 @@
         <v>92</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>104</v>
@@ -10509,7 +10514,7 @@
         <v>135</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>20</v>
@@ -10520,14 +10525,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10549,16 +10554,16 @@
         <v>203</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
@@ -10583,13 +10588,13 @@
         <v>20</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>20</v>
@@ -10607,7 +10612,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10625,27 +10630,27 @@
         <v>20</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10668,19 +10673,19 @@
         <v>20</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>20</v>
@@ -10729,7 +10734,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10750,10 +10755,10 @@
         <v>20</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>20</v>
@@ -10764,10 +10769,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10793,13 +10798,13 @@
         <v>203</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10825,11 +10830,11 @@
         <v>20</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>20</v>
@@ -10847,7 +10852,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10865,27 +10870,27 @@
         <v>20</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10911,16 +10916,16 @@
         <v>203</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>20</v>
@@ -10945,11 +10950,11 @@
         <v>20</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>20</v>
@@ -10967,7 +10972,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10988,10 +10993,10 @@
         <v>20</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>20</v>
@@ -11002,10 +11007,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11028,16 +11033,16 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11087,7 +11092,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11105,27 +11110,27 @@
         <v>20</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11148,16 +11153,16 @@
         <v>20</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11207,7 +11212,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11225,27 +11230,27 @@
         <v>20</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11268,19 +11273,19 @@
         <v>20</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>20</v>
@@ -11329,7 +11334,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11341,7 +11346,7 @@
         <v>20</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>20</v>
@@ -11350,10 +11355,10 @@
         <v>20</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>20</v>
@@ -11364,10 +11369,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11390,13 +11395,13 @@
         <v>20</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11447,7 +11452,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11471,7 +11476,7 @@
         <v>20</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>20</v>
@@ -11482,10 +11487,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11514,7 +11519,7 @@
         <v>139</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>141</v>
@@ -11567,7 +11572,7 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11591,7 +11596,7 @@
         <v>20</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>20</v>
@@ -11602,14 +11607,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11631,10 +11636,10 @@
         <v>138</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>141</v>
@@ -11689,7 +11694,7 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11724,10 +11729,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11750,13 +11755,13 @@
         <v>20</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11807,7 +11812,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11816,7 +11821,7 @@
         <v>92</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>104</v>
@@ -11828,10 +11833,10 @@
         <v>20</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>20</v>
@@ -11842,10 +11847,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11868,13 +11873,13 @@
         <v>20</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11925,7 +11930,7 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11934,7 +11939,7 @@
         <v>92</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>104</v>
@@ -11946,10 +11951,10 @@
         <v>20</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>20</v>
@@ -11960,10 +11965,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11989,16 +11994,16 @@
         <v>203</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>20</v>
@@ -12026,10 +12031,10 @@
         <v>116</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>20</v>
@@ -12047,7 +12052,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12065,13 +12070,13 @@
         <v>20</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>20</v>
@@ -12082,10 +12087,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12111,16 +12116,16 @@
         <v>203</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>20</v>
@@ -12145,13 +12150,13 @@
         <v>20</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>20</v>
@@ -12169,7 +12174,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12187,13 +12192,13 @@
         <v>20</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>20</v>
@@ -12204,10 +12209,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12230,17 +12235,17 @@
         <v>20</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>20</v>
@@ -12289,7 +12294,7 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12313,7 +12318,7 @@
         <v>20</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>20</v>
@@ -12324,10 +12329,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12350,13 +12355,13 @@
         <v>20</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12407,7 +12412,7 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12428,10 +12433,10 @@
         <v>20</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>20</v>
@@ -12442,10 +12447,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12468,16 +12473,16 @@
         <v>93</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12527,7 +12532,7 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12548,10 +12553,10 @@
         <v>20</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>20</v>
@@ -12562,10 +12567,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12588,16 +12593,16 @@
         <v>93</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12647,7 +12652,7 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12668,10 +12673,10 @@
         <v>20</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>20</v>
@@ -12682,10 +12687,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12708,19 +12713,19 @@
         <v>93</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>20</v>
@@ -12769,7 +12774,7 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12790,10 +12795,10 @@
         <v>20</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>20</v>
@@ -12804,10 +12809,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12830,13 +12835,13 @@
         <v>20</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12887,7 +12892,7 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12911,7 +12916,7 @@
         <v>20</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>20</v>
@@ -12922,10 +12927,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12954,7 +12959,7 @@
         <v>139</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N88" t="s" s="2">
         <v>141</v>
@@ -13007,7 +13012,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13031,7 +13036,7 @@
         <v>20</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>20</v>
@@ -13042,14 +13047,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -13071,10 +13076,10 @@
         <v>138</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>141</v>
@@ -13129,7 +13134,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13164,10 +13169,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13193,16 +13198,16 @@
         <v>203</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>20</v>
@@ -13227,13 +13232,13 @@
         <v>20</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>295</v>
+        <v>650</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>20</v>
@@ -13251,7 +13256,7 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>92</v>
@@ -13269,16 +13274,16 @@
         <v>20</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>388</v>
+        <v>300</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>649</v>
+        <v>301</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>650</v>
+        <v>302</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>20</v>
@@ -13286,10 +13291,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13312,19 +13317,19 @@
         <v>93</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>439</v>
+        <v>655</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>20</v>
@@ -13373,7 +13378,7 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13391,27 +13396,27 @@
         <v>20</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13437,16 +13442,16 @@
         <v>203</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>20</v>
@@ -13471,13 +13476,13 @@
         <v>20</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>20</v>
@@ -13495,7 +13500,7 @@
         <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13504,7 +13509,7 @@
         <v>92</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>104</v>
@@ -13519,7 +13524,7 @@
         <v>135</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>20</v>
@@ -13530,14 +13535,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13559,16 +13564,16 @@
         <v>203</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>20</v>
@@ -13593,13 +13598,13 @@
         <v>20</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>20</v>
@@ -13617,7 +13622,7 @@
         <v>20</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13635,27 +13640,27 @@
         <v>20</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13681,16 +13686,16 @@
         <v>82</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>20</v>
@@ -13739,7 +13744,7 @@
         <v>20</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13760,10 +13765,10 @@
         <v>20</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>20</v>

--- a/docs/StructureDefinition-PASportObservationSoftLeanMass.xlsx
+++ b/docs/StructureDefinition-PASportObservationSoftLeanMass.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T13:32:15+08:00</t>
+    <t>2026-04-03T21:17:06+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationSoftLeanMass.xlsx
+++ b/docs/StructureDefinition-PASportObservationSoftLeanMass.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T21:17:06+08:00</t>
+    <t>2026-06-25T08:48:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
